--- a/fixtures/C_ALPHA/filled.xlsx
+++ b/fixtures/C_ALPHA/filled.xlsx
@@ -36522,7 +36522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36600,82 +36600,94 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>template_spec_version</t>
+          <t>cedant_spec_hash</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>97b7356383303a8b9492eff451d9b9eb7c78afbb31a9dffb0100437f50ea26bb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>generator_version</t>
+          <t>template_spec_version</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ws0-1</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>issue_date</t>
+          <t>generator_version</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>ws0-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>issue_date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AED</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>premium_basis</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>AED</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>n_inputs</t>
+          <t>premium_basis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>NET</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>n_inputs</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>n_refer</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>12</t>
         </is>

--- a/fixtures/C_ALPHA/filled.xlsx
+++ b/fixtures/C_ALPHA/filled.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>One row per option (and per key where the factor varies by network / plan / TPA, else ANY). Enter the factor; the row marked Reference = Y is the option the base assumes and must read 1.0, exactly one per key (a key without its own reference row uses the ANY row's).</t>
+          <t>One row per option (and per key where the factor varies by network / plan / TPA, else ANY). Enter the factor; the row marked Reference = Y is the option the base assumes and should read 1.0 (another value is kept and warned), exactly one per key (a key without its own reference row uses the ANY row's).</t>
         </is>
       </c>
     </row>
